--- a/STEAMEE_Gap_Analysis.xlsx
+++ b/STEAMEE_Gap_Analysis.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="GAP ANALYSIS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GAP ANALYSIS" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -524,11 +524,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I166"/>
+  <dimension ref="A1:I206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
@@ -8340,6 +8340,1886 @@
         </is>
       </c>
     </row>
+    <row r="167" ht="42" customHeight="1">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>[Portal] [D01] User Acquisition</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Acquisition</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Portal Backend APIs</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Option 1 (Portal): New customers; New customer orders; AOV (first order); First-order item mix; Spend-to-new ratio (if spend joined)</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Requires custom Portal DB endpoints and frontend UI for: User Acquisition.</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="inlineStr">
+        <is>
+          <t>Yes (custom API)</t>
+        </is>
+      </c>
+      <c r="I167" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="42" customHeight="1">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>[Metabase] [D01] User Acquisition</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Acquisition</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Metabase SQL Query / Postgres</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 (Metabase): New customers; New customer orders; AOV (first order); First-order item mix; Spend-to-new ratio (if spend joined)</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>None. Directly query Postgres read-replica.</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I168" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="42" customHeight="1">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>[Portal] [D02] User Conversion Funnel</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Conversion</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>MoEngage Events</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Option 1 (Portal): Visitors; Signups; Profiles created; First orders; Step conversion %; Overall visit-to-order %</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>None (MoEngage tracked)</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I169" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="42" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>[Metabase] [D02] User Conversion Funnel</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Conversion</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>MoEngage Events</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 (Metabase): Visitors; Signups; Profiles created; First orders; Step conversion %; Overall visit-to-order %</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>None (MoEngage tracked)</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I170" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="42" customHeight="1">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>[Portal] [D03] Retention &amp; RFM</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Retention</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>Portal Backend APIs</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Option 1 (Portal): Cohort retention rate (M0..Mn); Active rate; RFM scores (R,F,M 1-5); RFM segment sizes; repeat rate by segment</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Requires custom Portal DB endpoints and frontend UI for: Retention &amp; RFM.</t>
+        </is>
+      </c>
+      <c r="H171" s="4" t="inlineStr">
+        <is>
+          <t>Yes (custom API)</t>
+        </is>
+      </c>
+      <c r="I171" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="42" customHeight="1">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>[Metabase] [D03] Retention &amp; RFM</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Retention</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Metabase SQL Query / Postgres</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 (Metabase): Cohort retention rate (M0..Mn); Active rate; RFM scores (R,F,M 1-5); RFM segment sizes; repeat rate by segment</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>None. Directly query Postgres read-replica.</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I172" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="42" customHeight="1">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>[Portal] [D04] Order Flow — New vs Repeat</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Acquisition</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Portal Backend APIs</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Option 1 (Portal): Total orders; New-customer orders; Repeat-customer orders; New:Repeat ratio; % repeat orders</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Requires custom Portal DB endpoints and frontend UI for: Order Flow — New vs Repeat.</t>
+        </is>
+      </c>
+      <c r="H173" s="4" t="inlineStr">
+        <is>
+          <t>Yes (custom API)</t>
+        </is>
+      </c>
+      <c r="I173" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="42" customHeight="1">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>[Metabase] [D04] Order Flow — New vs Repeat</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Acquisition</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Metabase SQL Query / Postgres</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 (Metabase): Total orders; New-customer orders; Repeat-customer orders; New:Repeat ratio; % repeat orders</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>None. Directly query Postgres read-replica.</t>
+        </is>
+      </c>
+      <c r="H174" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I174" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="42" customHeight="1">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>[Portal] [D05] Customer Lifetime Value (CLTV)</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Monetization</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>Portal Backend APIs</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>Option 1 (Portal): Historical CLTV (avg &amp; by segment); Avg orders per customer; Avg revenue per customer; CLTV by RFM segment; CLTV:CAC (if spend joined)</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>Requires custom Portal DB endpoints and frontend UI for: Customer Lifetime Value (CLTV).</t>
+        </is>
+      </c>
+      <c r="H175" s="4" t="inlineStr">
+        <is>
+          <t>Yes (custom API)</t>
+        </is>
+      </c>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="42" customHeight="1">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>[Metabase] [D05] Customer Lifetime Value (CLTV)</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Monetization</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>D05</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Metabase SQL Query / Postgres</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 (Metabase): Historical CLTV (avg &amp; by segment); Avg orders per customer; Avg revenue per customer; CLTV by RFM segment; CLTV:CAC (if spend joined)</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>None. Directly query Postgres read-replica.</t>
+        </is>
+      </c>
+      <c r="H176" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I176" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="42" customHeight="1">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>[Portal] [D06] Repeat Purchase Gap / Order Velocity</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Retention</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Portal Backend APIs</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Option 1 (Portal): Median &amp; avg gap 1-&gt;2, 2-&gt;3, 3-&gt;4; % reaching 2nd/3rd/4th order; distribution of inter-order intervals</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Requires custom Portal DB endpoints and frontend UI for: Repeat Purchase Gap / Order Velocity.</t>
+        </is>
+      </c>
+      <c r="H177" s="4" t="inlineStr">
+        <is>
+          <t>Yes (custom API)</t>
+        </is>
+      </c>
+      <c r="I177" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="42" customHeight="1">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>[Metabase] [D06] Repeat Purchase Gap / Order Velocity</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Retention</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Metabase SQL Query / Postgres</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 (Metabase): Median &amp; avg gap 1-&gt;2, 2-&gt;3, 3-&gt;4; % reaching 2nd/3rd/4th order; distribution of inter-order intervals</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>None. Directly query Postgres read-replica.</t>
+        </is>
+      </c>
+      <c r="H178" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I178" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="42" customHeight="1">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>[Portal] [D07] Customer Lifecycle Stage</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Retention</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>D07</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Portal Backend APIs</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>Option 1 (Portal): Count &amp; % of base per stage: Lead, New, Active, Repeat/Loyal, At-risk, Dormant, Reactivated; stage migration over time</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Requires custom Portal DB endpoints and frontend UI for: Customer Lifecycle Stage.</t>
+        </is>
+      </c>
+      <c r="H179" s="4" t="inlineStr">
+        <is>
+          <t>Yes (custom API)</t>
+        </is>
+      </c>
+      <c r="I179" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="42" customHeight="1">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>[Metabase] [D07] Customer Lifecycle Stage</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Retention</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>D07</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Metabase SQL Query / Postgres</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 (Metabase): Count &amp; % of base per stage: Lead, New, Active, Repeat/Loyal, At-risk, Dormant, Reactivated; stage migration over time</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>None. Directly query Postgres read-replica.</t>
+        </is>
+      </c>
+      <c r="H180" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I180" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="42" customHeight="1">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>[Portal] [D08] Revenue</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Monetization</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Portal Backend APIs</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>Option 1 (Portal): Total revenue; New vs Repeat revenue; AOV; Revenue per active customer; revenue by source/city/store; MoM/ YoY growth</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>Requires custom Portal DB endpoints and frontend UI for: Revenue.</t>
+        </is>
+      </c>
+      <c r="H181" s="4" t="inlineStr">
+        <is>
+          <t>Yes (custom API)</t>
+        </is>
+      </c>
+      <c r="I181" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="42" customHeight="1">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>[Metabase] [D08] Revenue</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Monetization</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>D08</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Metabase SQL Query / Postgres</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 (Metabase): Total revenue; New vs Repeat revenue; AOV; Revenue per active customer; revenue by source/city/store; MoM/ YoY growth</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>None. Directly query Postgres read-replica.</t>
+        </is>
+      </c>
+      <c r="H182" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I182" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="42" customHeight="1">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>[Portal] [D09] Marketing Efficiency — CAC, ROAS &amp; Spend</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Efficiency</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>D09</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>Portal Backend APIs</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>Option 1 (Portal): Spend (Meta/Google/total); Blended &amp; channel CAC; ROAS; CLTV:CAC; CAC payback (months); cost per install; cost per first order</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>Requires custom Portal DB endpoints and frontend UI for: Marketing Efficiency — CAC, ROAS &amp; Spend.</t>
+        </is>
+      </c>
+      <c r="H183" s="4" t="inlineStr">
+        <is>
+          <t>Yes (custom API)</t>
+        </is>
+      </c>
+      <c r="I183" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="42" customHeight="1">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>[Metabase] [D09] Marketing Efficiency — CAC, ROAS &amp; Spend</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Efficiency</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>D09</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Metabase SQL Query / Postgres</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 (Metabase): Spend (Meta/Google/total); Blended &amp; channel CAC; ROAS; CLTV:CAC; CAC payback (months); cost per install; cost per first order</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>None. Directly query Postgres read-replica.</t>
+        </is>
+      </c>
+      <c r="H184" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I184" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="42" customHeight="1">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>[Portal] [D10] Cohort Revenue &amp; Payback</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Efficiency</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>Portal Backend APIs</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>Option 1 (Portal): Cohort cumulative revenue (M0..Mn); cohort size; revenue per customer over time; months-to-payback; LTV curve</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>Requires custom Portal DB endpoints and frontend UI for: Cohort Revenue &amp; Payback.</t>
+        </is>
+      </c>
+      <c r="H185" s="4" t="inlineStr">
+        <is>
+          <t>Yes (custom API)</t>
+        </is>
+      </c>
+      <c r="I185" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="42" customHeight="1">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>[Metabase] [D10] Cohort Revenue &amp; Payback</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Efficiency</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>Metabase SQL Query / Postgres</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 (Metabase): Cohort cumulative revenue (M0..Mn); cohort size; revenue per customer over time; months-to-payback; LTV curve</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>None. Directly query Postgres read-replica.</t>
+        </is>
+      </c>
+      <c r="H186" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I186" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="42" customHeight="1">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>[Portal] [D11] Store Performance Scorecard</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Store &amp; Geo</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>D11</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>Portal Backend APIs</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>Option 1 (Portal): Per store: orders, revenue, new vs repeat, AOV, retention rate, CAC, SV customers vs 500 target, MoM growth; red/amber/green flags</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>Requires custom Portal DB endpoints and frontend UI for: Store Performance Scorecard.</t>
+        </is>
+      </c>
+      <c r="H187" s="4" t="inlineStr">
+        <is>
+          <t>Yes (custom API)</t>
+        </is>
+      </c>
+      <c r="I187" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="42" customHeight="1">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>[Metabase] [D11] Store Performance Scorecard</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Store &amp; Geo</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>D11</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Metabase SQL Query / Postgres</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 (Metabase): Per store: orders, revenue, new vs repeat, AOV, retention rate, CAC, SV customers vs 500 target, MoM growth; red/amber/green flags</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>None. Directly query Postgres read-replica.</t>
+        </is>
+      </c>
+      <c r="H188" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I188" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="42" customHeight="1">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>[Portal] [D12] Super Value (SV) Customer Tracker</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Store &amp; Geo</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>Portal Backend APIs</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>Option 1 (Portal): SV customers per store; SV vs 500 target &amp; % complete; net new SV per month; SV by source; SV run-rate vs plan</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>Requires custom Portal DB endpoints and frontend UI for: Super Value (SV) Customer Tracker.</t>
+        </is>
+      </c>
+      <c r="H189" s="4" t="inlineStr">
+        <is>
+          <t>Yes (custom API)</t>
+        </is>
+      </c>
+      <c r="I189" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="42" customHeight="1">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>[Metabase] [D12] Super Value (SV) Customer Tracker</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Store &amp; Geo</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>Metabase SQL Query / Postgres</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 (Metabase): SV customers per store; SV vs 500 target &amp; % complete; net new SV per month; SV by source; SV run-rate vs plan</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>None. Directly query Postgres read-replica.</t>
+        </is>
+      </c>
+      <c r="H190" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I190" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="42" customHeight="1">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>[Portal] [D13] Channel &amp; Attribution Source-of-Truth</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Foundation</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>MoEngage Events</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>Option 1 (Portal): Orders &amp; revenue by channel; channel mix %; % orders missing source; reconciliation vs finance; data-freshness lag</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>None (MoEngage tracked)</t>
+        </is>
+      </c>
+      <c r="H191" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I191" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="42" customHeight="1">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>[Metabase] [D13] Channel &amp; Attribution Source-of-Truth</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Foundation</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>MoEngage Events</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 (Metabase): Orders &amp; revenue by channel; channel mix %; % orders missing source; reconciliation vs finance; data-freshness lag</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>None (MoEngage tracked)</t>
+        </is>
+      </c>
+      <c r="H192" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I192" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="42" customHeight="1">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>[Portal] [D14] Churn &amp; Win-back / Reactivation</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Retention</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>D14</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>MoEngage Events</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>Option 1 (Portal): Churn rate; at-risk count; dormant count; reactivation rate; revenue recovered; win-back campaign ROI</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>None (MoEngage tracked)</t>
+        </is>
+      </c>
+      <c r="H193" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I193" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="42" customHeight="1">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>[Metabase] [D14] Churn &amp; Win-back / Reactivation</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Retention</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>D14</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>MoEngage Events</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 (Metabase): Churn rate; at-risk count; dormant count; reactivation rate; revenue recovered; win-back campaign ROI</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>None (MoEngage tracked)</t>
+        </is>
+      </c>
+      <c r="H194" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I194" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="42" customHeight="1">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>[Portal] [D15] WhatsApp Funnel</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Conversion</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>MoEngage Events</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>Option 1 (Portal): CTWA clicks; conversations started; qualified leads; orders; step conversion %; cost per WA order</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>None (MoEngage tracked)</t>
+        </is>
+      </c>
+      <c r="H195" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I195" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="42" customHeight="1">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>[Metabase] [D15] WhatsApp Funnel</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Conversion</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>MoEngage Events</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 (Metabase): CTWA clicks; conversations started; qualified leads; orders; step conversion %; cost per WA order</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>None (MoEngage tracked)</t>
+        </is>
+      </c>
+      <c r="H196" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I196" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="42" customHeight="1">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>[Portal] [D16] Campaign &amp; Promo / Offer Performance</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Efficiency</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>MoEngage Events</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>Option 1 (Portal): Orders/revenue with vs without offer; redemption rate; discount value; incremental orders; new vs repeat on offer; campaign-level ROI</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>None (MoEngage tracked)</t>
+        </is>
+      </c>
+      <c r="H197" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I197" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="42" customHeight="1">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>[Metabase] [D16] Campaign &amp; Promo / Offer Performance</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Efficiency</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>MoEngage Events</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 (Metabase): Orders/revenue with vs without offer; redemption rate; discount value; incremental orders; new vs repeat on offer; campaign-level ROI</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>None (MoEngage tracked)</t>
+        </is>
+      </c>
+      <c r="H198" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I198" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="42" customHeight="1">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>[Portal] [D17] AOV &amp; Basket / Item Mix</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Monetization</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>Portal Backend APIs</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>Option 1 (Portal): AOV; items per order; revenue/ orders by garment category; category attach rate; AOV trend</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>Requires custom Portal DB endpoints and frontend UI for: AOV &amp; Basket / Item Mix.</t>
+        </is>
+      </c>
+      <c r="H199" s="4" t="inlineStr">
+        <is>
+          <t>Yes (custom API)</t>
+        </is>
+      </c>
+      <c r="I199" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="42" customHeight="1">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>[Metabase] [D17] AOV &amp; Basket / Item Mix</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Monetization</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>Metabase SQL Query / Postgres</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 (Metabase): AOV; items per order; revenue/ orders by garment category; category attach rate; AOV trend</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>None. Directly query Postgres read-replica.</t>
+        </is>
+      </c>
+      <c r="H200" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I200" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="42" customHeight="1">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>[Portal] [D18] City / Geo Expansion</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Store &amp; Geo</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>D18</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>Portal Backend APIs</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>Option 1 (Portal): Customers/orders/revenue per city; new-customer density; store coverage; growth by city; CAC by city</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>Requires custom Portal DB endpoints and frontend UI for: City / Geo Expansion.</t>
+        </is>
+      </c>
+      <c r="H201" s="4" t="inlineStr">
+        <is>
+          <t>Yes (custom API)</t>
+        </is>
+      </c>
+      <c r="I201" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="42" customHeight="1">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>[Metabase] [D18] City / Geo Expansion</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Store &amp; Geo</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>D18</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>Metabase SQL Query / Postgres</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 (Metabase): Customers/orders/revenue per city; new-customer density; store coverage; growth by city; CAC by city</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>None. Directly query Postgres read-replica.</t>
+        </is>
+      </c>
+      <c r="H202" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I202" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="42" customHeight="1">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>[Portal] [D19] Executive Marketing MIS (North-Star)</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Executive</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>D19</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>Portal Backend APIs</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>Option 1 (Portal): New customers; CAC; CLTV:CAC; repeat rate; revenue &amp; growth; ROAS; SV progress; retention — all vs target &amp; prior period</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>Requires custom Portal DB endpoints and frontend UI for: Executive Marketing MIS (North-Star).</t>
+        </is>
+      </c>
+      <c r="H203" s="4" t="inlineStr">
+        <is>
+          <t>Yes (custom API)</t>
+        </is>
+      </c>
+      <c r="I203" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="42" customHeight="1">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>[Metabase] [D19] Executive Marketing MIS (North-Star)</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Executive</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>D19</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>Metabase SQL Query / Postgres</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 (Metabase): New customers; CAC; CLTV:CAC; repeat rate; revenue &amp; growth; ROAS; SV progress; retention — all vs target &amp; prior period</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>None. Directly query Postgres read-replica.</t>
+        </is>
+      </c>
+      <c r="H204" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I204" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="42" customHeight="1">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>[Portal] [D20] Data Health &amp; Instrumentation QA</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Foundation</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>D20</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>MoEngage Events</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>Option 1 (Portal): Event coverage %; channel coverage (App/WA/Call); % orders missing source/store; data freshness/lag; row-count anomalies</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>None (MoEngage tracked)</t>
+        </is>
+      </c>
+      <c r="H205" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I205" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="42" customHeight="1">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>[Metabase] [D20] Data Health &amp; Instrumentation QA</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>Marketing - Foundation</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>D20</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>MoEngage Events</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>Option 2 (Metabase): Event coverage %; channel coverage (App/WA/Call); % orders missing source/store; data freshness/lag; row-count anomalies</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>None (MoEngage tracked)</t>
+        </is>
+      </c>
+      <c r="H206" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I206" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
